--- a/南寧高中學生名冊_範例.xlsx
+++ b/南寧高中學生名冊_範例.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>陳大同</t>
+          <t>蘇大輔</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>林小華</t>
+          <t>賴小祥</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>王小明</t>
+          <t>蘇小祥</t>
         </is>
       </c>
     </row>
@@ -522,29 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>張美玲</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>999005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>李鐵雄</t>
+          <t>賴大寶</t>
         </is>
       </c>
     </row>
